--- a/output/excel/Safehold 2024 10-K (1) 1_classified.xlsx
+++ b/output/excel/Safehold 2024 10-K (1) 1_classified.xlsx
@@ -564,223 +564,223 @@
       <c r="C7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Total real estate, net and real estate-related intangible assets, net and real estate available and held for sale</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>910,507</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>924,761</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Real estate, at cost</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>740,971</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>744,337</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Loans receivable, net - related party ($2,311 and $2,429 of allowances as of December 31, 2024 and 2023, respectively)</t>
+          <t xml:space="preserve">      Less: accumulated depreciation</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>112,359</t>
+          <t>(46,428)</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>112,111</t>
+          <t>(40,400)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Equity investments</t>
+          <t xml:space="preserve">      Real estate, net</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>250,034</t>
+          <t>694,543</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>310,320</t>
+          <t>703,937</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Cash and cash equivalents</t>
+          <t xml:space="preserve">   Real estate-related intangible assets, net</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>8,346</t>
+          <t>208,731</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>18,761</t>
+          <t>211,113</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Restricted cash</t>
+          <t xml:space="preserve">   Real estate available and held for sale</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>8,772</t>
+          <t>7,233</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>27,979</t>
+          <t>9,711</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Deferred tax asset, net</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>5,222</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>7,619</t>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Total real estate, net and real estate-related intangible assets, net and real estate available and held for sale</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>910,507</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>924,761</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Deferred operating lease income receivable</t>
+          <t xml:space="preserve">   Loans receivable, net - related party ($2,311 and $2,429 of allowances as of December 31, 2024 and 2023, respectively)</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>210,773</t>
+          <t>112,359</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>180,032</t>
+          <t>112,111</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Deferred expenses and other assets, net(2)</t>
+          <t xml:space="preserve">   Equity investments</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>105,015</t>
+          <t>250,034</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>89,238</t>
+          <t>310,320</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Real estate, at cost</t>
+          <t xml:space="preserve">   Cash and cash equivalents</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>740,971</t>
+          <t>8,346</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>744,337</t>
+          <t>18,761</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Less: accumulated depreciation</t>
+          <t xml:space="preserve">   Restricted cash</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>(46,428)</t>
+          <t>8,772</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>(40,400)</t>
+          <t>27,979</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Real estate, net</t>
+          <t xml:space="preserve">   Deferred tax asset, net</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>694,543</t>
+          <t>5,222</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>703,937</t>
+          <t>7,619</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Real estate-related intangible assets, net</t>
+          <t xml:space="preserve">   Deferred operating lease income receivable</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>208,731</t>
+          <t>210,773</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>211,113</t>
+          <t>180,032</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Real estate available and held for sale</t>
+          <t xml:space="preserve">   Deferred expenses and other assets, net(2)</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>7,233</t>
+          <t>105,015</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>9,711</t>
+          <t>89,238</t>
         </is>
       </c>
     </row>
@@ -820,234 +820,233 @@
       <c r="C23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Total liabilities</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>4,525,352</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>4,252,638</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Accounts payable, accrued expenses and other liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>$ 144,991</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>$ 134,518</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Commitments and contingencies (refer to Note 10)</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr"/>
-      <c r="C25" s="8" t="inlineStr"/>
+          <t xml:space="preserve">      Real estate-related intangible liabilities, net</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>62,922</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>63,755</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Redeemable noncontrolling interests (refer to Note 3)</t>
+          <t xml:space="preserve">      Debt obligations, net</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,317,439</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>19,011</t>
+          <t>4,054,365</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Equity:</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr"/>
-      <c r="C27" s="6" t="inlineStr"/>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Total liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>4,525,352</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>4,252,638</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Total equity</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>2,374,027</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>2,276,665</t>
-        </is>
-      </c>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Commitments and contingencies (refer to Note 10)</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr"/>
+      <c r="C28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Accounts payable, accrued expenses and other liabilities</t>
+          <t xml:space="preserve">   Redeemable noncontrolling interests (refer to Note 3)</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>$ 144,991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>$ 134,518</t>
+          <t>19,011</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Real estate-related intangible liabilities, net</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>62,922</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>63,755</t>
-        </is>
-      </c>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Equity:</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr"/>
+      <c r="C30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Debt obligations, net</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>4,317,439</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>4,054,365</t>
-        </is>
-      </c>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Safehold Inc. shareholders' equity:</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Safehold Inc. shareholders' equity:</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr"/>
-      <c r="C32" s="6" t="inlineStr"/>
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         Common stock, $0.01 par value, 400,000 shares authorized, 71,440 and 71,077 shares issued and outstanding as of December 31, 2024 and 2023, respectively</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Total Safehold Inc. shareholders' equity</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>2,344,018</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>2,231,253</t>
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         Additional paid-in capital</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>2,191,840</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>2,184,299</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Noncontrolling interests</t>
+          <t xml:space="preserve">         Retained earnings</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>30,009</t>
+          <t>102,472</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>45,412</t>
+          <t>47,580</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Common stock, $0.01 par value, 400,000 shares authorized, 71,440 and 71,077 shares issued and outstanding as of December 31,
-2024 and 2023, respectively</t>
+          <t xml:space="preserve">         Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>48,992</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>(1,337)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         Additional paid-in capital</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>2,191,840</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>2,184,299</t>
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Total Safehold Inc. shareholders' equity</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>2,344,018</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>2,231,253</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Retained earnings</t>
+          <t xml:space="preserve">      Noncontrolling interests</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>102,472</t>
+          <t>30,009</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>47,580</t>
+          <t>45,412</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         Accumulated other comprehensive income (loss)</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>48,992</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>(1,337)</t>
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Total equity</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>2,374,027</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>2,276,665</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1094,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Safehold Inc. Consolidated Statements of Operations (In thousands, except per share data) — Safehold Inc.  (in In thousands, except per share data)</t>
+          <t>Safehold Inc. Consolidated Statements of Operations (In thousands, except per share data) — Safehold Inc.  (in thousands, except per share data)</t>
         </is>
       </c>
     </row>
@@ -1631,19 +1630,31 @@
       <c r="D28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Weighted average number of common shares:</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr"/>
-      <c r="C29" s="6" t="inlineStr"/>
-      <c r="D29" s="6" t="inlineStr"/>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Basic</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>$ 1.48</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>$ (0.82)</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>$ 2.17</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Basic</t>
+          <t xml:space="preserve">      Diluted</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1663,26 +1674,14 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Diluted</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>$ 1.48</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>$ (0.82)</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>$ 2.17</t>
-        </is>
-      </c>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Weighted average number of common shares:</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="inlineStr"/>
+      <c r="D31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -1791,7 +1790,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Net income (loss)</t>
+          <t xml:space="preserve">   Net income (loss)</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -1823,7 +1822,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Reclassification of (gains) losses on derivatives into earnings(1)</t>
+          <t xml:space="preserve">   Reclassification of (gains) losses on derivatives into earnings(1)</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -1845,7 +1844,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on derivatives</t>
+          <t xml:space="preserve">   Unrealized gain (loss) on derivatives</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -1867,7 +1866,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss):</t>
+          <t xml:space="preserve">   Other comprehensive income (loss):</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -1911,7 +1910,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Comprehensive (income) loss attributable to noncontrolling interests</t>
+          <t xml:space="preserve">   Comprehensive (income) loss attributable to noncontrolling interests</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -1931,22 +1930,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Comprehensive income (loss) attributable to Safehold Inc.</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Comprehensive income (loss) attributable to Safehold Inc.</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>$ 156,092</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>$ (59,591)</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>$ 179,684</t>
         </is>
@@ -2030,42 +2029,42 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Balance at December 31, 2021</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Balance at December 31, 2021</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>$—</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>$566</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>$1,663,324</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>$59,368</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>$(40,980)</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>2,924</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>$1,685,202</t>
         </is>
@@ -2074,7 +2073,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Net income (loss)</t>
+          <t xml:space="preserve">   Net income (loss)</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -2116,7 +2115,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Issuance of common stock, net / amortization</t>
+          <t xml:space="preserve">   Issuance of common stock, net / amortization</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -2158,7 +2157,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Dividends declared ($0.701 per share)</t>
+          <t xml:space="preserve">   Dividends declared ($0.701 per share)</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -2200,7 +2199,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Change in accumulated other comprehensive income (loss)</t>
+          <t xml:space="preserve">   Change in accumulated other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -2242,7 +2241,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Distributions to noncontrolling interests</t>
+          <t xml:space="preserve">   Distributions to noncontrolling interests</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -2284,7 +2283,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Contributions from noncontrolling interests</t>
+          <t xml:space="preserve">   Contributions from noncontrolling interests</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -2326,7 +2325,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Additional paid in capital attributable to redeemable noncontrolling interests</t>
+          <t xml:space="preserve">   Additional paid in capital attributable to redeemable noncontrolling interests</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -2366,42 +2365,42 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Balance at December 31, 2022</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Balance at December 31, 2022</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>$19,011</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>$624</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>$ 1,986,417</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>$1,986,417</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>$151,226</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>$3,281</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>$4,056</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>$2,145,604</t>
         </is>
@@ -2410,7 +2409,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Impact from adoption of new accounting standard (refer to Note 3)</t>
+          <t xml:space="preserve">   Impact from adoption of new accounting standard (refer to Note 3)</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -2452,7 +2451,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Net income (loss)</t>
+          <t xml:space="preserve">   Net income (loss)</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -2494,7 +2493,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Issuance of common stock, net / amortization</t>
+          <t xml:space="preserve">   Issuance of common stock, net / amortization</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -2536,7 +2535,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Dividends declared ($0.708 per share)</t>
+          <t xml:space="preserve">   Dividends declared ($0.708 per share)</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -2578,7 +2577,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Change in accumulated other comprehensive income (loss)</t>
+          <t xml:space="preserve">   Change in accumulated other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2620,7 +2619,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Contributions from noncontrolling interests</t>
+          <t xml:space="preserve">   Contributions from noncontrolling interests</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2662,7 +2661,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Distributions to noncontrolling interests</t>
+          <t xml:space="preserve">   Distributions to noncontrolling interests</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2704,7 +2703,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Merger consideration (refer to Note 1 and Note 3)</t>
+          <t xml:space="preserve">   Merger consideration (refer to Note 1 and Note 3)</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2744,42 +2743,42 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Balance at December 31, 2023</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Balance at December 31, 2023</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>$19,011</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>$711</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>$ 2,184,299</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>$2,184,299</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>$47,580</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>$(1,337)</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>$45,412</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>$2,276,665</t>
         </is>
@@ -2788,7 +2787,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Net income (loss)</t>
+          <t xml:space="preserve">   Net income (loss)</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2830,7 +2829,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Issuance of common stock, net / amortization</t>
+          <t xml:space="preserve">   Issuance of common stock, net / amortization</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2872,7 +2871,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Dividends declared ($0.708 per share)</t>
+          <t xml:space="preserve">   Dividends declared ($0.708 per share)</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2914,7 +2913,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Change in accumulated other comprehensive income (loss)</t>
+          <t xml:space="preserve">   Change in accumulated other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2956,7 +2955,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Contributions from noncontrolling interests, net</t>
+          <t xml:space="preserve">   Contributions from noncontrolling interests, net</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2998,7 +2997,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Distributions to noncontrolling interests</t>
+          <t xml:space="preserve">   Distributions to noncontrolling interests</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -3040,7 +3039,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Acquisition of noncontrolling interest</t>
+          <t xml:space="preserve">   Acquisition of noncontrolling interest</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3082,7 +3081,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Redemption of noncontrolling interest</t>
+          <t xml:space="preserve">   Redemption of noncontrolling interest</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -3122,42 +3121,42 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Balance at December 31, 2024</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Balance at December 31, 2024</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>$—</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>$714</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>$2,191,840</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>$102,472</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>$48,992</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>$30,009</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>$2,374,027</t>
         </is>
@@ -3177,7 +3176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3265,261 +3264,273 @@
       <c r="D6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Changes in assets and liabilities:</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Depreciation and amortization</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>9,947</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>9,936</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>9,613</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Cash flows provided by (used in) operating activities</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>37,855</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>15,391</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>64,852</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Stock-based compensation expense</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>13,757</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>23,230</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>1,546</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Depreciation and amortization</t>
+          <t xml:space="preserve">      Deferred operating lease income</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>9,947</t>
+          <t>(30,740)</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>9,936</t>
+          <t>(31,163)</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>9,613</t>
+          <t>(31,558)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Stock-based compensation expense</t>
+          <t xml:space="preserve">      Non-cash interest income from sales-type leases</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>13,757</t>
+          <t>(91,855)</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>23,230</t>
+          <t>(83,780)</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>1,546</t>
+          <t>(73,991)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Deferred operating lease income</t>
+          <t xml:space="preserve">      Non-cash interest expense</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>(30,740)</t>
+          <t>14,701</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>(31,163)</t>
+          <t>15,070</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>(31,558)</t>
+          <t>13,641</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Non-cash interest income from sales-type leases</t>
+          <t xml:space="preserve">      Amortization of real estate-related intangibles, net</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>(91,855)</t>
+          <t>2,310</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>(83,780)</t>
+          <t>2,306</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>(73,991)</t>
+          <t>2,305</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Non-cash interest expense</t>
+          <t xml:space="preserve">      Impairment of goodwill</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>14,701</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>15,070</t>
+          <t>145,365</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>13,641</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Amortization of real estate-related intangibles, net</t>
+          <t xml:space="preserve">      Provision for credit losses</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>2,310</t>
+          <t>9,489</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>2,306</t>
+          <t>2,704</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>2,305</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Impairment of goodwill</t>
+          <t xml:space="preserve">      Earnings from equity method investments</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(22,977)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>145,365</t>
+          <t>(24,229)</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(9,055)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Provision for credit losses</t>
+          <t xml:space="preserve">      Distributions from operations of equity method investments</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>9,489</t>
+          <t>12,870</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>2,704</t>
+          <t>8,003</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,047</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Earnings from equity method investments</t>
+          <t xml:space="preserve">      Gain on sale of Ground Leases</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>(22,977)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>(24,229)</t>
+          <t>(447)</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>(9,055)</t>
+          <t>(55,811)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Distributions from operations of equity method investments</t>
+          <t xml:space="preserve">      Amortization of premium, discount and deferred financing costs on debt obligations, net</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>12,870</t>
+          <t>7,426</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>8,003</t>
+          <t>7,288</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>2,047</t>
+          <t>5,384</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Gain on sale of Ground Leases</t>
+          <t xml:space="preserve">      Non-cash management fees</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3529,1184 +3540,132 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>(447)</t>
+          <t>5,199</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>(55,811)</t>
+          <t>20,252</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Amortization of premium, discount and deferred financing costs on debt obligations, net</t>
+          <t xml:space="preserve">      Other income recognized from derivative transaction (refer to Note 11)</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>7,426</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>7,288</t>
+          <t>(15,191)</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>5,384</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Non-cash management fees</t>
+          <t xml:space="preserve">      Other operating activities</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(7,021)</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>5,199</t>
+          <t>(1,448)</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>20,252</t>
+          <t>4,677</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Other income recognized from derivative transaction (refer to Note 11)</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>(15,191)</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Changes in assets and liabilities:</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr"/>
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Other operating activities</t>
+          <t xml:space="preserve">      Changes in deferred expenses and other assets, net</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>(7,021)</t>
+          <t>5,263</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>(1,448)</t>
+          <t>13,080</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>4,677</t>
+          <t>11,044</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Changes in deferred expenses and other assets, net</t>
+          <t xml:space="preserve">      Changes in accounts payable, accrued expenses and other liabilities</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>5,263</t>
+          <t>8,070</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>13,080</t>
+          <t>(5,967)</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>11,044</t>
+          <t>20,074</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Changes in accounts payable, accrued expenses and other liabilities</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>8,070</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>(5,967)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>20,074</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Cash flows from investing activities:</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr"/>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Acquisitions of real estate</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>(13,078)</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Origination/acquisition of net investment in sales-type leases and Ground Lease receivables</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>(304,283)</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>(316,755)</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>(1,278,406)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Origination of loans receivable, net</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>(114,450)</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Payment for merger consideration</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>(88,685)</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Cash and cash equivalents acquired upon merger</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>3,213</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Contributions to equity method investments</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>(10,049)</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>(52,479)</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>(7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Distributions from equity method investments</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>52,425</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Funding reserves received from Ground Lease tenant net of disbursements</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>(297)</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Net proceeds from sale of Ground Leases</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>4,200</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>135,529</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Net proceeds received from sale of real estate available and held for sale</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>5,764</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>1,631</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Return of deposits on Ground Lease investments</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>2,049</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>1,171</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>(2,250)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Return of cash collateral for debt obligations</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>19,112</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Funding of cash collateral for debt obligations</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>(19,112)</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Payments to acquire derivative transactions</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>(8,780)</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Proceeds received from derivative transactions</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>11,067</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>8,022</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Proceeds received from the settlement of derivative transactions</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>32,052</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Other investing activities</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>(1,395)</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>(285)</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>(1,115)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Cash flows provided by (used in) investing activities</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>(212,370)</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>(576,572)</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>(1,145,953)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Cash flows from financing activities:</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr"/>
-      <c r="C45" s="6" t="inlineStr"/>
-      <c r="D45" s="6" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Proceeds from issuance of common stock</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>151,940</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>309,160</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Proceeds from debt obligations</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>2,271,584</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>577,000</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>1,830,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Repayments of debt obligations</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>(2,008,000)</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>(150,000)</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>(1,005,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Payments for deferred financing costs</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>(24,192)</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>(4,615)</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>(5,136)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Dividends paid to common shareholders</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>(50,589)</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>(46,039)</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>(42,187)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Payment of offering costs</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>(51)</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>(8,099)</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>(5,190)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Payments for withholding taxes upon vesting for stock-based compensation</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>(5,102)</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>(970)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Redemption of redeemable noncontrolling interests</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>(18,435)</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Distributions to noncontrolling interests</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>(925)</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>(651)</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>(8,549)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Contributions from noncontrolling interests</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>29,002</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>40,132</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>19,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Acquisition of noncontrolling interest</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>(48,399)</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Other financing activities</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>(137)</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>(153)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Cash flows provided by (used in) financing activities</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>144,893</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>559,531</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>1,090,975</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>Changes in cash, cash equivalents and restricted cash</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>(29,622)</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="inlineStr">
-        <is>
-          <t>(1,650)</t>
-        </is>
-      </c>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>9,874</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>Cash, cash equivalents and restricted cash at beginning of period</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>46,740</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>48,390</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>38,516</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>Cash, cash equivalents and restricted cash at end of period</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>$ 17,118</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>$ 46,740</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>$ 48,390</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>Reconciliation of cash and cash equivalents and restricted cash presented on the consolidated statements of cash flows</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr"/>
-      <c r="C62" s="6" t="inlineStr"/>
-      <c r="D62" s="6" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>$ 8,346</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>$ 18,761</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>$ 20,066</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Restricted cash</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>8,772</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>27,979</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>28,324</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Total cash and cash equivalents and restricted cash</t>
-        </is>
-      </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t>$ 17,118</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t>$ 46,740</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>$ 48,390</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>Supplemental disclosure of cash flow information:</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr"/>
-      <c r="C66" s="6" t="inlineStr"/>
-      <c r="D66" s="6" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Cash paid for interest</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>$ 162,375</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>$ 151,263</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>$ 93,853</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>Supplemental disclosure of non-cash investing and financing activity:</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr"/>
-      <c r="C68" s="6" t="inlineStr"/>
-      <c r="D68" s="6" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Debt obligations assumed (refer to Note 3)</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>$ —</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>$ 99,995</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>$ —</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Issuance of common stock for acquisition of assets (refer to Note 3)</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>35,588</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Dividends declared to common shareholders</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>12,954</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>13,033</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>11,050</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Non-cash interest accrued to debt balances</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>4,163</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>4,055</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>1,988</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Accrued finance costs</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Accrued offering costs</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Real estate transferred to real estate available and held for sale</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>3,366</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Cash flows provided by (used in) operating activities</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>37,855</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>15,391</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>64,852</t>
         </is>
       </c>
     </row>
